--- a/data/trans_camb/IP16B02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 47,76</t>
+          <t>-28,83; 51,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 52,22</t>
+          <t>-25,05; 52,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-51,58; 6,14</t>
+          <t>-55,09; 6,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-58,76; 5,87</t>
+          <t>-61,24; 1,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 10,87</t>
+          <t>-32,31; 11,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 8,94</t>
+          <t>-34,76; 10,45</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 122,44</t>
+          <t>-31,04; 150,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,71; 128,09</t>
+          <t>-26,39; 128,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,33; 6,54</t>
+          <t>-57,25; 6,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 6,29</t>
+          <t>-61,88; 1,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 12,97</t>
+          <t>-35,48; 13,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 10,67</t>
+          <t>-38,18; 13,08</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 0,0</t>
+          <t>-42,97; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -6,66</t>
+          <t>-60,61; -6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 0,0</t>
+          <t>-39,77; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,1; -3,5</t>
+          <t>-32,89; -3,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,45; -3,24</t>
+          <t>-32,74; -3,15</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 0,0</t>
+          <t>-42,97; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -6,66</t>
+          <t>-60,61; -6,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 0,0</t>
+          <t>-39,77; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,1; -3,5</t>
+          <t>-32,89; -3,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,45; -3,24</t>
+          <t>-32,74; -3,15</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 69,22</t>
+          <t>-10,4; 75,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 76,26</t>
+          <t>-10,91; 75,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 52,21</t>
+          <t>-14,03; 49,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 65,49</t>
+          <t>7,27; 66,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 49,84</t>
+          <t>-2,39; 48,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 53,87</t>
+          <t>5,62; 57,82</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 500,69</t>
+          <t>-13,91; 498,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 625,31</t>
+          <t>-13,0; 335,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 124,91</t>
+          <t>-15,75; 117,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 188,88</t>
+          <t>7,84; 195,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 123,35</t>
+          <t>-1,79; 124,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 134,92</t>
+          <t>8,2; 146,83</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 32,16</t>
+          <t>-11,86; 31,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 36,25</t>
+          <t>-4,37; 34,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 20,45</t>
+          <t>-16,51; 21,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 19,89</t>
+          <t>-21,2; 21,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 18,43</t>
+          <t>-9,75; 18,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 20,57</t>
+          <t>-6,0; 21,34</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 56,06</t>
+          <t>-12,66; 52,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 63,32</t>
+          <t>-4,71; 55,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 28,25</t>
+          <t>-17,78; 30,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 28,86</t>
+          <t>-24,02; 30,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 25,47</t>
+          <t>-10,71; 25,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 28,21</t>
+          <t>-6,67; 29,31</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-41,44; 11,96</t>
+          <t>-42,01; 12,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 7,91</t>
+          <t>-46,08; 15,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 21,95</t>
+          <t>-8,94; 23,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,64</t>
+          <t>0,0; 30,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,04; 7,92</t>
+          <t>-25,5; 7,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 5,43</t>
+          <t>-28,63; 6,88</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 13,65</t>
+          <t>-43,19; 16,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 7,75</t>
+          <t>-49,75; 13,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 28,53</t>
+          <t>-8,95; 29,29</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,49</t>
+          <t>0,0; 44,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 9,65</t>
+          <t>-26,48; 8,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 6,09</t>
+          <t>-30,68; 7,53</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 0,0</t>
+          <t>-53,91; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 0,0</t>
+          <t>-68,09; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 0,0</t>
+          <t>-37,08; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 0,0</t>
+          <t>-36,85; 0,0</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 0,0</t>
+          <t>-53,91; 0,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1502,17 +1502,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-65,79; 0,0</t>
+          <t>-68,09; 0,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 0,0</t>
+          <t>-37,08; 0,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 0,0</t>
+          <t>-36,85; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 10,9</t>
+          <t>-12,94; 12,2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 13,33</t>
+          <t>-12,39; 13,58</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 8,9</t>
+          <t>-10,4; 8,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 10,89</t>
+          <t>-8,77; 9,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 5,31</t>
+          <t>-9,08; 5,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 7,27</t>
+          <t>-7,63; 7,34</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 14,6</t>
+          <t>-14,38; 16,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 17,5</t>
+          <t>-13,55; 18,3</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 10,88</t>
+          <t>-10,92; 9,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 12,89</t>
+          <t>-9,28; 11,63</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 6,5</t>
+          <t>-10,07; 6,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 8,86</t>
+          <t>-8,4; 8,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B02-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 51,8</t>
+          <t>-30,55; 46,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 52,19</t>
+          <t>-26,75; 51,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 6,08</t>
+          <t>-55,2; 6,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-61,24; 1,55</t>
+          <t>-61,16; 2,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 11,45</t>
+          <t>-32,95; 9,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 10,45</t>
+          <t>-36,76; 10,23</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 150,22</t>
+          <t>-33,12; 112,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 128,29</t>
+          <t>-27,84; 116,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,25; 6,48</t>
+          <t>-56,0; 6,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 1,8</t>
+          <t>-66,83; 2,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 13,85</t>
+          <t>-35,76; 12,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 13,08</t>
+          <t>-39,81; 12,18</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 0,0</t>
+          <t>-38,98; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -6,63</t>
+          <t>-64,43; -6,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,89; -3,5</t>
+          <t>-29,98; -3,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,74; -3,15</t>
+          <t>-33,25; -3,24</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 0,0</t>
+          <t>-38,98; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -6,63</t>
+          <t>-64,43; -6,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,89; -3,5</t>
+          <t>-29,98; -3,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-32,74; -3,15</t>
+          <t>-33,25; -3,24</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 75,14</t>
+          <t>-14,03; 74,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 75,28</t>
+          <t>-12,54; 76,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 49,19</t>
+          <t>-11,74; 51,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 66,2</t>
+          <t>7,11; 58,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 48,74</t>
+          <t>-2,81; 49,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 57,82</t>
+          <t>6,56; 55,28</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 498,87</t>
+          <t>-15,63; 530,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 335,68</t>
+          <t>-13,45; 600,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 117,07</t>
+          <t>-11,89; 131,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,84; 195,66</t>
+          <t>7,64; 139,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 124,66</t>
+          <t>-3,42; 120,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,2; 146,83</t>
+          <t>9,26; 148,48</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 31,85</t>
+          <t>-13,29; 29,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 34,86</t>
+          <t>-5,56; 35,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 21,21</t>
+          <t>-16,19; 20,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 21,24</t>
+          <t>-24,04; 18,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 18,15</t>
+          <t>-10,05; 18,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 21,34</t>
+          <t>-6,08; 22,57</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 52,75</t>
+          <t>-13,72; 47,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 55,77</t>
+          <t>-5,82; 61,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 30,87</t>
+          <t>-17,65; 28,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 30,13</t>
+          <t>-25,74; 23,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 25,13</t>
+          <t>-10,7; 26,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 29,31</t>
+          <t>-6,75; 31,58</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-42,01; 12,54</t>
+          <t>-43,16; 13,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 15,72</t>
+          <t>-46,09; 10,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 23,21</t>
+          <t>-8,94; 31,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,58</t>
+          <t>0,0; 29,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 7,39</t>
+          <t>-24,43; 6,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 6,88</t>
+          <t>-28,03; 7,77</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 16,33</t>
+          <t>-45,28; 16,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,75; 13,98</t>
+          <t>-48,76; 9,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 29,29</t>
+          <t>-8,96; 45,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,22</t>
+          <t>0,0; 42,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 8,69</t>
+          <t>-25,12; 7,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 7,53</t>
+          <t>-29,64; 8,88</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 0,0</t>
+          <t>-50,29; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 0,0</t>
+          <t>-65,02; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 0,0</t>
+          <t>-34,99; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 0,0</t>
+          <t>-36,51; 0,0</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 0,0</t>
+          <t>-50,29; 0,0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1502,17 +1502,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 0,0</t>
+          <t>-65,02; 0,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 0,0</t>
+          <t>-34,99; 0,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 0,0</t>
+          <t>-36,51; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 12,2</t>
+          <t>-13,78; 11,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 13,58</t>
+          <t>-11,65; 13,99</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 8,35</t>
+          <t>-9,28; 8,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 9,84</t>
+          <t>-9,42; 9,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 5,55</t>
+          <t>-9,01; 5,32</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 7,34</t>
+          <t>-7,99; 7,58</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,38; 16,5</t>
+          <t>-15,12; 15,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 18,3</t>
+          <t>-12,97; 19,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 9,99</t>
+          <t>-10,12; 9,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 11,63</t>
+          <t>-9,9; 12,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 6,75</t>
+          <t>-9,91; 6,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 8,7</t>
+          <t>-8,77; 9,1</t>
         </is>
       </c>
     </row>
